--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104489_W4.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104489_W4.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5579</v>
+        <v>3.8754</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8935</v>
+        <v>2.9215</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6644</v>
+        <v>0.9539</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1114</v>
+        <v>0.1161</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.2613</v>
+        <v>-1.2527</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3727</v>
+        <v>1.3688</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0184</v>
+        <v>1.9917</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.551</v>
+        <v>-0.5623</v>
       </c>
       <c r="L2" t="n">
-        <v>2.5694</v>
+        <v>2.554</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.907</v>
+        <v>-1.8756</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7103</v>
+        <v>-0.6904</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2606</v>
+        <v>-0.9432</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6563</v>
+        <v>-0.5859</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6042999999999999</v>
+        <v>-0.3573</v>
       </c>
       <c r="V2" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="W2" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0438</v>
+        <v>2.2218</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9929</v>
+        <v>1.3278</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0509</v>
+        <v>0.894</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.6457</v>
+        <v>-1.6446</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1343</v>
+        <v>-0.1295</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.5114</v>
+        <v>-1.5151</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0182</v>
+        <v>-0.0412</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5124</v>
+        <v>0.5031</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5306</v>
+        <v>-0.5443</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6275</v>
+        <v>-1.6034</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P3" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3285</v>
+        <v>-0.4994</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5989</v>
+        <v>-0.0375</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2704</v>
+        <v>-0.4618</v>
       </c>
       <c r="V3" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W3" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.24</v>
+        <v>1.8556</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3899</v>
+        <v>0.4024</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8502</v>
+        <v>1.4532</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3488</v>
+        <v>-0.3582</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3998</v>
+        <v>1.3906</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.7486</v>
+        <v>-1.7488</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2864</v>
+        <v>1.2436</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7796</v>
+        <v>1.7507</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4932</v>
+        <v>-0.5071</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6352</v>
+        <v>-1.6018</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3798</v>
+        <v>-0.3601</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2554</v>
+        <v>-1.2417</v>
       </c>
       <c r="P4" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R4" t="n">
-        <v>3.8562</v>
+        <v>3.8697</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9575</v>
+        <v>-1.3309</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5867</v>
+        <v>-0.5162</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3708</v>
+        <v>-0.8147</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7463</v>
+        <v>0.7277</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1344</v>
+        <v>-0.2022</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8807</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5841</v>
+        <v>-0.5905</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2871</v>
+        <v>1.2867</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8712</v>
+        <v>-1.8772</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0679</v>
+        <v>-0.0881</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2165</v>
+        <v>2.2063</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.2844</v>
+        <v>-2.2945</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5162</v>
+        <v>-0.5023</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P5" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0305</v>
+        <v>-0.0476</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1603</v>
+        <v>0.1136</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1909</v>
+        <v>-0.1612</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4437</v>
+        <v>0.4779</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0149</v>
+        <v>-0.0152</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4586</v>
+        <v>0.4931</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3533</v>
+        <v>0.3559</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0014</v>
+        <v>0.0028</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3519</v>
+        <v>0.3531</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0546</v>
+        <v>0.0545</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2986</v>
+        <v>0.3014</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1364</v>
+        <v>-0.1057</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0668</v>
+        <v>-0.0359</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. FISCHER</t>
+          <t>R. NETO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3869</v>
+        <v>-0.7834</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7628</v>
+        <v>0.9052</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6241</v>
+        <v>-1.6886</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2134</v>
+        <v>0.363</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7705</v>
+        <v>-0.396</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5570000000000001</v>
+        <v>0.759</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5750999999999999</v>
+        <v>1.8822</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4258</v>
+        <v>0.4234</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1493</v>
+        <v>1.4588</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3617</v>
+        <v>-1.5193</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3446</v>
+        <v>-0.8194</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7779</v>
+        <v>-0.9478</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0212</v>
+        <v>-0.3836</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7991</v>
+        <v>-0.5642</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.4102</v>
+        <v>-1.792</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.2249</v>
+        <v>0.5447</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1853</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. NETO</t>
+          <t>L. FISCHER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5486</v>
+        <v>-1.6635</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3664</v>
+        <v>-1.1339</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.915</v>
+        <v>-0.5296</v>
       </c>
       <c r="G8" t="n">
-        <v>0.386</v>
+        <v>0.2243</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3895</v>
+        <v>0.7752</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7755</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9281</v>
+        <v>0.5659</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4462</v>
+        <v>0.4169</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4818</v>
+        <v>0.1489</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.542</v>
+        <v>-0.3416</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8357</v>
+        <v>0.3583</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7227</v>
+        <v>-1.0731</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9739</v>
+        <v>-0.3324</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7489</v>
+        <v>-0.7407</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.7997</v>
+        <v>-2.4082</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5463</v>
+        <v>-0.2292</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.3461</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="9">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9701</v>
+        <v>-2.0559</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8632</v>
+        <v>-1.6891</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1068</v>
+        <v>-0.3668</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7827</v>
+        <v>-1.7706</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9351</v>
+        <v>-0.9308</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8476</v>
+        <v>-0.8398</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0883</v>
+        <v>-0.0946</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.163</v>
+        <v>-0.1691</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6944</v>
+        <v>-1.6759</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1963</v>
+        <v>0.1032</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0302</v>
+        <v>0.1599</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2265</v>
+        <v>-0.0567</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0276</v>
+        <v>-2.3413</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7645</v>
+        <v>-2.0654</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2631</v>
+        <v>-0.2759</v>
       </c>
       <c r="G10" t="n">
         <v>0.1358</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4343</v>
+        <v>0.4337</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2985</v>
+        <v>-0.2979</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4312</v>
+        <v>0.4225</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1429</v>
+        <v>1.1376</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2954</v>
+        <v>-0.2866</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7086</v>
+        <v>-0.7039</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R10" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2241</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2994</v>
+        <v>0.0161</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.1078</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9183</v>
+        <v>-2.5739</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8744</v>
+        <v>-2.7564</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0439</v>
+        <v>0.1825</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5912</v>
+        <v>-1.5881</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.378</v>
+        <v>-1.3813</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2132</v>
+        <v>-0.2068</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5013</v>
+        <v>-1.5203</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.424</v>
+        <v>-1.4381</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0898</v>
+        <v>-0.0678</v>
       </c>
       <c r="N11" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9545</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2389</v>
+        <v>-0.098</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7156</v>
+        <v>-0.5315</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.9604</v>
+        <v>-1.9497</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.9604</v>
+        <v>-1.9497</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2871</v>
+        <v>-4.0716</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4936</v>
+        <v>-2.3386</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7935</v>
+        <v>-1.7331</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.2006</v>
+        <v>-2.2054</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.313</v>
+        <v>-1.3207</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-0.8847</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4257</v>
+        <v>-1.4466</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.714</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7749</v>
+        <v>-0.7588</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2906</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0302</v>
+        <v>0.1599</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2604</v>
+        <v>-0.2309</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.2495</v>
+        <v>-2.2504</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0965</v>
+        <v>0.0863</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.2865</v>
+        <v>-6.3657</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.8985</v>
+        <v>-5.1709</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.388</v>
+        <v>-1.1947</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.0696</v>
+        <v>-3.0785</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0548</v>
+        <v>-0.0573</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.0148</v>
+        <v>-3.0212</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.458</v>
+        <v>-1.4896</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4187</v>
+        <v>0.403</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.8767</v>
+        <v>-1.8925</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6116</v>
+        <v>-1.589</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R13" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.285</v>
+        <v>-1.3554</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9739</v>
+        <v>-0.1955</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3111</v>
+        <v>-1.16</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-11.3934</v>
+        <v>-10.6969</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.1636</v>
+        <v>-9.8148</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2296</v>
+        <v>-0.8821000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-10.0228</v>
+        <v>-10.0408</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.5729</v>
+        <v>-1.5793</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.4498</v>
+        <v>-8.461500000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7344</v>
+        <v>1.48</v>
       </c>
       <c r="K14" t="n">
-        <v>4.107399999999999</v>
+        <v>3.9573</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.3732</v>
+        <v>-2.4775</v>
       </c>
       <c r="M14" t="n">
-        <v>-11.7571</v>
+        <v>-11.5207</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.6804</v>
+        <v>-5.5366</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.076700000000002</v>
+        <v>-5.983900000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>11.3415</v>
+        <v>11.3815</v>
       </c>
       <c r="Q14" t="n">
-        <v>-15.8785</v>
+        <v>-15.9343</v>
       </c>
       <c r="R14" t="n">
-        <v>27.2199</v>
+        <v>27.3157</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.666800000000001</v>
+        <v>-6.9922</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.4799</v>
+        <v>-1.7693</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.1871</v>
+        <v>-5.2227</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.045300000000001</v>
+        <v>-5.0456</v>
       </c>
       <c r="W14" t="n">
-        <v>6.459899999999999</v>
+        <v>6.4087</v>
       </c>
       <c r="X14" t="n">
-        <v>-11.5054</v>
+        <v>-11.4542</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>14.8866</v>
+        <v>14.1862</v>
       </c>
       <c r="E15" t="n">
-        <v>11.378</v>
+        <v>10.6266</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5086</v>
+        <v>3.5596</v>
       </c>
       <c r="G15" t="n">
-        <v>6.8235</v>
+        <v>6.8295</v>
       </c>
       <c r="H15" t="n">
-        <v>5.9811</v>
+        <v>5.977</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8424</v>
+        <v>0.8525</v>
       </c>
       <c r="J15" t="n">
-        <v>6.286</v>
+        <v>6.2521</v>
       </c>
       <c r="K15" t="n">
-        <v>6.2513</v>
+        <v>6.2225</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0346</v>
+        <v>0.0296</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5375</v>
+        <v>0.5775</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2702</v>
+        <v>-0.2455</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8078</v>
+        <v>0.8229</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1972</v>
+        <v>1.4948</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5606</v>
+        <v>0.8589</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.636</v>
       </c>
       <c r="V15" t="n">
-        <v>3.8243</v>
+        <v>3.8132</v>
       </c>
       <c r="W15" t="n">
-        <v>3.9851</v>
+        <v>3.9709</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7397</v>
+        <v>3.0388</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1111</v>
+        <v>-0.6263</v>
       </c>
       <c r="F16" t="n">
-        <v>3.6286</v>
+        <v>3.6651</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9836</v>
+        <v>-0.9988</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.8151</v>
+        <v>-1.8206</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8316</v>
+        <v>0.8218</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.5524</v>
+        <v>-1.5875</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.8698</v>
+        <v>-0.8866000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6825</v>
+        <v>-0.7009</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5688</v>
+        <v>0.5887</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9453</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>1.5141</v>
+        <v>1.5228</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6177</v>
+        <v>1.9174</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8903</v>
+        <v>1.1888</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7274</v>
+        <v>0.7286</v>
       </c>
       <c r="V16" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0758</v>
+        <v>2.9873</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7732</v>
+        <v>3.5576</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6974</v>
+        <v>-0.5703</v>
       </c>
       <c r="G17" t="n">
-        <v>5.0547</v>
+        <v>5.0497</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4776</v>
+        <v>1.4763</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5771</v>
+        <v>3.5734</v>
       </c>
       <c r="J17" t="n">
-        <v>5.8482</v>
+        <v>5.8202</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4475</v>
+        <v>1.4339</v>
       </c>
       <c r="L17" t="n">
-        <v>4.4007</v>
+        <v>4.3863</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7935</v>
+        <v>-0.7704</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.09619999999999999</v>
+        <v>0.8269</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5383</v>
+        <v>0.29</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4422</v>
+        <v>0.5369</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9595</v>
+        <v>2.4537</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3179</v>
+        <v>0.2191</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2774</v>
+        <v>2.2347</v>
       </c>
       <c r="G18" t="n">
-        <v>2.0417</v>
+        <v>2.0419</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1168</v>
+        <v>1.1199</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9249000000000001</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2406</v>
+        <v>1.2067</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0248</v>
+        <v>1.0062</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2158</v>
+        <v>0.2004</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8011</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>0.092</v>
+        <v>0.1137</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7091</v>
+        <v>0.7215</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.083</v>
+        <v>-4.0974</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9097</v>
+        <v>1.4101</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1785</v>
+        <v>0.7731</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7313</v>
+        <v>0.6371</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8227</v>
+        <v>0.8228</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.5234</v>
+        <v>-1.5139</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8435</v>
+        <v>1.3453</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3624</v>
+        <v>0.9308</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4811</v>
+        <v>0.4145</v>
       </c>
       <c r="G19" t="n">
-        <v>3.9292</v>
+        <v>3.9336</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1255</v>
+        <v>0.129</v>
       </c>
       <c r="I19" t="n">
-        <v>3.8037</v>
+        <v>3.8045</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2004</v>
+        <v>4.1897</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6927</v>
+        <v>0.6895</v>
       </c>
       <c r="L19" t="n">
-        <v>3.5078</v>
+        <v>3.5003</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2712</v>
+        <v>-0.2562</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1352</v>
+        <v>0.3613</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2087</v>
+        <v>0.3831</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0735</v>
+        <v>-0.0218</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3627</v>
+        <v>-1.3562</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3627</v>
+        <v>-1.3562</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SORIANO</t>
+          <t>E. STEVENSON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2486</v>
+        <v>-0.4555</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7161999999999999</v>
+        <v>0.2267</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4676</v>
+        <v>-0.6822</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0071</v>
+        <v>-0.251</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0403</v>
+        <v>0.4565</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0475</v>
+        <v>-0.7075</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0658</v>
+        <v>0.0922</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0835</v>
+        <v>0.8446</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1493</v>
+        <v>-0.7524</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0729</v>
+        <v>-0.3432</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1238</v>
+        <v>-0.3881</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1967</v>
+        <v>0.0449</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.9488</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.8562</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5632</v>
+        <v>0.202</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8207</v>
+        <v>0.1345</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7425</v>
+        <v>0.0675</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1441</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1093</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. STEVENSON</t>
+          <t>M. SPISSU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4175</v>
+        <v>-0.9</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4685</v>
+        <v>-1.9686</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8859</v>
+        <v>1.0685</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2545</v>
+        <v>-1.3024</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4545</v>
+        <v>-0.4486</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.709</v>
+        <v>-0.8538</v>
       </c>
       <c r="J21" t="n">
-        <v>0.09950000000000001</v>
+        <v>-1.0322</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8485</v>
+        <v>0.2273</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.749</v>
+        <v>-1.2595</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.354</v>
+        <v>-0.2703</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.394</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>0.04</v>
+        <v>0.4057</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6805</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.8697</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2492</v>
+        <v>0.7469</v>
       </c>
       <c r="T21" t="n">
-        <v>0.369</v>
+        <v>0.5966</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1198</v>
+        <v>0.1503</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0927</v>
+        <v>2.6147</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="22">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0011</v>
+        <v>-1.4046</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8115</v>
+        <v>-0.4673</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1897</v>
+        <v>-0.9373</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9252</v>
+        <v>-0.9105</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1358</v>
+        <v>-1.1236</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2106</v>
+        <v>0.2131</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1854</v>
+        <v>-0.1953</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.6345</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7398</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7794</v>
+        <v>-0.2078</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3992</v>
+        <v>-0.0444</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3802</v>
+        <v>-0.1634</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.977</v>
+        <v>-0.9692</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.977</v>
+        <v>-0.9692</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SPISSU</t>
+          <t>J. SORIANO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3569</v>
+        <v>-2.0135</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9858</v>
+        <v>-2.0435</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6289</v>
+        <v>0.0301</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3067</v>
+        <v>-0.9906</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.459</v>
+        <v>0.0457</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8477</v>
+        <v>-1.0363</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0069</v>
+        <v>0.052</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2353</v>
+        <v>-0.0969</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2423</v>
+        <v>0.1489</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2998</v>
+        <v>-1.0426</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6944</v>
+        <v>0.1426</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3946</v>
+        <v>-1.1852</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7238</v>
+        <v>0.7981</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4688</v>
+        <v>0.5269</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.255</v>
+        <v>0.2711</v>
       </c>
       <c r="V23" t="n">
-        <v>2.6224</v>
+        <v>1.1383</v>
       </c>
       <c r="W23" t="n">
-        <v>2.3461</v>
+        <v>1.2472</v>
       </c>
       <c r="X23" t="n">
-        <v>0.2763</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.0878</v>
+        <v>-7.0541</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.1683</v>
+        <v>-7.7094</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0805</v>
+        <v>0.6554</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.3494</v>
+        <v>-3.3606</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.2131</v>
+        <v>-4.2324</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8637</v>
+        <v>0.8718</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.2387</v>
+        <v>-3.2771</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.236</v>
+        <v>-3.2695</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.0027</v>
+        <v>-0.0077</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1107</v>
+        <v>-0.0835</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9771</v>
+        <v>-0.9629</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="Q24" t="n">
-        <v>-7.2586</v>
+        <v>-7.2842</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.929</v>
       </c>
       <c r="T24" t="n">
-        <v>0.983</v>
+        <v>0.5152</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1186</v>
+        <v>0.4138</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W24" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>11.3932</v>
+        <v>12.1836</v>
       </c>
       <c r="E25" t="n">
-        <v>3.093500000000002</v>
+        <v>2.7457</v>
       </c>
       <c r="F25" t="n">
-        <v>8.299700000000001</v>
+        <v>9.4381</v>
       </c>
       <c r="G25" t="n">
-        <v>10.0226</v>
+        <v>10.0408</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5728</v>
+        <v>1.5792</v>
       </c>
       <c r="I25" t="n">
-        <v>8.4498</v>
+        <v>8.461400000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>11.7571</v>
+        <v>11.5208</v>
       </c>
       <c r="K25" t="n">
-        <v>5.680299999999999</v>
+        <v>5.536500000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>6.0768</v>
+        <v>5.984200000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.7345</v>
+        <v>-1.48</v>
       </c>
       <c r="N25" t="n">
-        <v>-4.1076</v>
+        <v>-3.9572</v>
       </c>
       <c r="O25" t="n">
-        <v>2.3731</v>
+        <v>2.4775</v>
       </c>
       <c r="P25" t="n">
-        <v>-11.3416</v>
+        <v>-11.3816</v>
       </c>
       <c r="Q25" t="n">
-        <v>-27.2199</v>
+        <v>-27.3157</v>
       </c>
       <c r="R25" t="n">
-        <v>15.8782</v>
+        <v>15.934</v>
       </c>
       <c r="S25" t="n">
-        <v>7.6668</v>
+        <v>8.4787</v>
       </c>
       <c r="T25" t="n">
-        <v>5.1871</v>
+        <v>5.222700000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>2.479900000000001</v>
+        <v>3.2561</v>
       </c>
       <c r="V25" t="n">
-        <v>5.045299999999999</v>
+        <v>5.045500000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>13.3695</v>
+        <v>13.3177</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.324</v>
+        <v>-8.2722</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104489_W4.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104489_W4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-11.4542</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.07140000000000001</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.5139</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.3562</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0.278</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.9692</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104489_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-8.2722</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
